--- a/import_template_partner/tests/sample_with_credit_control.xlsx
+++ b/import_template_partner/tests/sample_with_credit_control.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="69">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -79,19 +79,13 @@
     <t xml:space="preserve">comment</t>
   </si>
   <si>
-    <t xml:space="preserve">customer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">supplier</t>
-  </si>
-  <si>
     <t xml:space="preserve">agent</t>
   </si>
   <si>
     <t xml:space="preserve">agent_type</t>
   </si>
   <si>
-    <t xml:space="preserve">commission</t>
+    <t xml:space="preserve">commission_id</t>
   </si>
   <si>
     <t xml:space="preserve">settlement</t>
@@ -100,7 +94,7 @@
     <t xml:space="preserve">user_id</t>
   </si>
   <si>
-    <t xml:space="preserve">invoice_group_method_id</t>
+    <t xml:space="preserve">sale_invoicing_grouping_criteria_id</t>
   </si>
   <si>
     <t xml:space="preserve">property_payment_term_id</t>
@@ -121,9 +115,6 @@
     <t xml:space="preserve">property_product_pricelist</t>
   </si>
   <si>
-    <t xml:space="preserve">supplier_pricelist_id</t>
-  </si>
-  <si>
     <t xml:space="preserve">ref</t>
   </si>
   <si>
@@ -179,9 +170,6 @@
   </si>
   <si>
     <t xml:space="preserve">Notes from tests.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">True</t>
   </si>
   <si>
     <t xml:space="preserve">Mitchell Admin</t>
@@ -249,7 +237,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot; €&quot;"/>
-    <numFmt numFmtId="167" formatCode="DD/MM/YY"/>
+    <numFmt numFmtId="167" formatCode="dd/mm/yy"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -348,23 +336,23 @@
     </xf>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3" customBuiltin="false"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6" customBuiltin="false"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AO6"/>
-  <sheetFormatPr defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AL6"/>
+  <sheetFormatPr defaultColWidth="8.89453125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.28"/>
@@ -374,37 +362,31 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="24.03"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="8.1"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="9" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="15.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="8.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="15.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="11.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="15" style="0" width="8.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="13.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="22.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="20" style="0" width="8.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="19.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="8.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="18.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="23.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="28.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="20.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="37.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="25.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="0" width="35.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="24.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="0" width="21.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="8.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="36.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="0" width="35.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="0" width="23.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="0" width="13.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="0" width="26.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="0" width="18.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1022" min="42" style="0" width="8.89"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1023" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="19.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="18.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="23.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="28.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="20.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="37.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="25.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="35.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="24.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="36.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="0" width="35.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="23.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="13.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="0" width="26.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="0" width="18.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1021" min="1020" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1022" style="0" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -483,7 +465,7 @@
       <c r="Z1" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="0" t="s">
+      <c r="AA1" s="3" t="s">
         <v>26</v>
       </c>
       <c r="AB1" s="0" t="s">
@@ -492,74 +474,65 @@
       <c r="AC1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="0" t="s">
+      <c r="AD1" s="3" t="s">
         <v>29</v>
       </c>
       <c r="AE1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" s="0" t="s">
         <v>31</v>
       </c>
       <c r="AG1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AH1" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="0" t="s">
+      <c r="AI1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AJ1" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="0" t="s">
+      <c r="AK1" s="3" t="s">
         <v>36</v>
       </c>
       <c r="AL1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="0" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L2" s="5"/>
       <c r="M2" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N2" s="0" t="n">
         <v>958958958</v>
@@ -568,53 +541,50 @@
         <v>666555666</v>
       </c>
       <c r="P2" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="S2" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="X2" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="Q2" s="0" t="s">
+      <c r="AF2" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="S2" s="0" t="s">
+      <c r="AH2" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="T2" s="0" t="s">
+      <c r="AI2" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ2" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="Z2" s="0" t="s">
+      <c r="AK2" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="AI2" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="AK2" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="AL2" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="AM2" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="AN2" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="AO2" s="6" t="n">
+      <c r="AL2" s="6" t="n">
         <v>44197</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -626,109 +596,103 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="T5" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH5" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI5" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ5" s="0" t="s">
         <v>53</v>
       </c>
       <c r="AK5" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="AL5" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="AM5" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="AN5" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="AO5" s="6" t="n">
+      <c r="AL5" s="6" t="n">
         <v>44197</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="T6" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI6" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ6" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="AL6" s="0" t="s">
+      <c r="AK6" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="AM6" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="AN6" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="AO6" s="6" t="n">
+      <c r="AL6" s="6" t="n">
         <v>44197</v>
       </c>
     </row>
